--- a/tests/golden/table.xlsx
+++ b/tests/golden/table.xlsx
@@ -492,359 +492,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>101846</colOff>
-      <row>14</row>
-      <rowOff>91457</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="圖片 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="883920" y="762000"/>
-          <a:ext cx="1587746" cy="1615457"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>490466</colOff>
-      <row>14</row>
-      <rowOff>91457</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="圖片 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="1173480" y="762000"/>
-          <a:ext cx="1587746" cy="1615457"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>137160</colOff>
-      <row>0</row>
-      <rowOff>286604</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>68580</colOff>
-      <row>0</row>
-      <rowOff>1272539</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="圖片 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="137160" y="286604"/>
-          <a:ext cx="777240" cy="985935"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>239006</colOff>
-      <row>16</row>
-      <rowOff>91457</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="圖片 2"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="845820" y="2438400"/>
-          <a:ext cx="1587746" cy="1615457"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>137160</colOff>
-      <row>0</row>
-      <rowOff>286605</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>1082040</colOff>
-      <row>0</row>
-      <rowOff>1211581</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="圖片 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="137160" y="286605"/>
-          <a:ext cx="944880" cy="924976"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>490466</colOff>
-      <row>28</row>
-      <rowOff>91457</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="圖片 3"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="845820" y="2438400"/>
-          <a:ext cx="1587746" cy="1615457"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>137160</colOff>
-      <row>0</row>
-      <rowOff>286605</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>1082040</colOff>
-      <row>0</row>
-      <rowOff>1249680</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="圖片 2"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="137160" y="286605"/>
-          <a:ext cx="944880" cy="963075"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>490466</colOff>
-      <row>26</row>
-      <rowOff>91457</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="圖片 3"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="1409700" y="3787140"/>
-          <a:ext cx="1587746" cy="1615457"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1553,9 +1200,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1704,9 +1350,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1863,9 +1508,8 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2496,11 +2140,10 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="3">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3211,12 +2854,11 @@
     <mergeCell ref="B1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="4">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>